--- a/Presupuesto-Personal-junio2026.xlsx
+++ b/Presupuesto-Personal-junio2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d86eecf8daf4f0d/Documents/SQL Server Management Studio 22/Tienda-sqlserver/EXCEL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d86eecf8daf4f0d/Documents/SQL Server Management Studio 22/Tienda-sqlserver/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{5918F4CC-6ECC-43D2-A22B-DAB448D65025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11772" windowHeight="12240" xr2:uid="{2C6BFFE3-BBBA-4E8F-B45B-4199BCCC55D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C6BFFE3-BBBA-4E8F-B45B-4199BCCC55D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -233,12 +233,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -247,14 +243,17 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1492,150 +1491,145 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2943C41E-CA90-4D15-8AD4-1CC940DC1155}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A2:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D3" s="3"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="9">
         <f>SUM(B5,B6)</f>
         <v>7500</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>2000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>2000</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="9">
         <f>SUM(B10:B14)</f>
         <v>5800</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="12"/>
+      <c r="B17" s="13"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <f>SUM(B5:B6)</f>
         <v>7500</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="6">
         <f>SUM(B10:B14)</f>
         <v>5800</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="10">
         <f>B18-B19</f>
         <v>1700</v>
       </c>
